--- a/data/trans_orig/IP28-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP28-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5361</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3263</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11087</t>
+          <t>10666</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91524</t>
+          <t>91400</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99447</t>
+          <t>99500</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>108926</t>
+          <t>108803</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>117172</t>
+          <t>117141</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>204086</t>
+          <t>204662</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>215311</t>
+          <t>215734</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>601</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>5868</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7736</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2790</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10406</t>
+          <t>10806</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15992</t>
+          <t>16582</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>10258</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21822</t>
+          <t>21786</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18909</t>
+          <t>18097</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>35281</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>208847</t>
+          <t>208169</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>226105</t>
+          <t>225364</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>209928</t>
+          <t>209430</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>226952</t>
+          <t>225560</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>423691</t>
+          <t>422013</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>446857</t>
+          <t>447970</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,89%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11193</t>
+          <t>11324</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23576</t>
+          <t>23839</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10189</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22651</t>
+          <t>23007</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24045</t>
+          <t>24678</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41898</t>
+          <t>42437</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>783</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7490</t>
+          <t>7211</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8736</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7118</t>
+          <t>7494</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18596</t>
+          <t>18128</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5882</t>
+          <t>5978</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16226</t>
+          <t>16289</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14817</t>
+          <t>15712</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29719</t>
+          <t>29869</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>89669</t>
+          <t>89927</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>105980</t>
+          <t>106072</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>101445</t>
+          <t>102223</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>117700</t>
+          <t>117092</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>195848</t>
+          <t>197399</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>219065</t>
+          <t>218151</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,0%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9903</t>
+          <t>9362</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21634</t>
+          <t>21840</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11271</t>
+          <t>10951</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23635</t>
+          <t>23125</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23552</t>
+          <t>23650</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41104</t>
+          <t>40636</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>641</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5385</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>663</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8251</t>
+          <t>8864</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10938</t>
+          <t>11524</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23596</t>
+          <t>24397</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19686</t>
+          <t>20359</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36009</t>
+          <t>35513</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35280</t>
+          <t>35657</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55731</t>
+          <t>56370</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>143085</t>
+          <t>143071</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>161487</t>
+          <t>161101</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>142715</t>
+          <t>142302</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>163075</t>
+          <t>162785</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>291822</t>
+          <t>291103</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>317780</t>
+          <t>318043</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,88%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13519</t>
+          <t>13767</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27418</t>
+          <t>26850</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14945</t>
+          <t>14790</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29402</t>
+          <t>29088</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>31052</t>
+          <t>31302</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>50491</t>
+          <t>50664</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>2077</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9455</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>4097</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13336</t>
+          <t>14191</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>32674</t>
+          <t>33044</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>54564</t>
+          <t>53773</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>43822</t>
+          <t>44446</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>67417</t>
+          <t>68344</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>83690</t>
+          <t>82871</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>114910</t>
+          <t>114159</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>549248</t>
+          <t>550624</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>580406</t>
+          <t>580529</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>578842</t>
+          <t>578478</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>610793</t>
+          <t>611044</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1137468</t>
+          <t>1139459</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1180860</t>
+          <t>1182272</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,29%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43328</t>
+          <t>42521</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>65220</t>
+          <t>64441</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>46351</t>
+          <t>45948</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>68799</t>
+          <t>69183</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>95083</t>
+          <t>95851</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>127917</t>
+          <t>126855</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>14519</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>14804</t>
+          <t>14795</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>11499</t>
+          <t>11918</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>25294</t>
+          <t>25424</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11466</t>
+          <t>11384</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7168</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5467</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15456</t>
+          <t>15502</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>114482</t>
+          <t>114347</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>125142</t>
+          <t>124605</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>116397</t>
+          <t>115839</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>126149</t>
+          <t>126049</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>234142</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>249239</t>
+          <t>248697</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7299</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8627</t>
+          <t>9089</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13446</t>
+          <t>12906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>5405</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7169</t>
+          <t>7661</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18653</t>
+          <t>19460</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>10060</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22274</t>
+          <t>22473</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19688</t>
+          <t>19873</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>36936</t>
+          <t>36823</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>171781</t>
+          <t>171848</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>189650</t>
+          <t>188645</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>202662</t>
+          <t>202629</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>220072</t>
+          <t>218961</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>380652</t>
+          <t>380784</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>404843</t>
+          <t>404535</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11029</t>
+          <t>11283</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24638</t>
+          <t>24839</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9031</t>
+          <t>9096</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21495</t>
+          <t>21600</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23203</t>
+          <t>22979</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41220</t>
+          <t>41690</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4341</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>706</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6588</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>4649</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13078</t>
+          <t>14185</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5745</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15796</t>
+          <t>15594</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11780</t>
+          <t>12111</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25648</t>
+          <t>25798</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>100273</t>
+          <t>100400</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>118912</t>
+          <t>118178</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>102969</t>
+          <t>103372</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>120275</t>
+          <t>120977</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>208286</t>
+          <t>209014</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>233672</t>
+          <t>234885</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,48%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17762</t>
+          <t>18345</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34021</t>
+          <t>34240</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15753</t>
+          <t>15422</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31263</t>
+          <t>30674</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38778</t>
+          <t>37837</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60153</t>
+          <t>59752</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>755</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>6595</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13669</t>
+          <t>12537</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23868</t>
+          <t>23740</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16860</t>
+          <t>17252</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31163</t>
+          <t>31920</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32420</t>
+          <t>31896</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>52646</t>
+          <t>51267</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>96322</t>
+          <t>96686</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>115243</t>
+          <t>116474</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>108497</t>
+          <t>108017</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>127193</t>
+          <t>126613</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>208178</t>
+          <t>210755</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>236834</t>
+          <t>238556</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,9%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19332</t>
+          <t>19056</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35458</t>
+          <t>34619</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14176</t>
+          <t>14018</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27145</t>
+          <t>27782</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>36631</t>
+          <t>35479</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>58588</t>
+          <t>56322</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11479</t>
+          <t>10770</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9890</t>
+          <t>10169</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18062</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34291</t>
+          <t>34683</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53471</t>
+          <t>55919</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>42196</t>
+          <t>40207</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>64227</t>
+          <t>63881</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>80736</t>
+          <t>80976</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>110641</t>
+          <t>111994</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>500896</t>
+          <t>501246</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>534753</t>
+          <t>533769</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>543220</t>
+          <t>547391</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>579138</t>
+          <t>581001</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1057299</t>
+          <t>1057769</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1104055</t>
+          <t>1103945</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,65%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>59177</t>
+          <t>59607</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>87172</t>
+          <t>87324</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>50645</t>
+          <t>50209</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>75891</t>
+          <t>74822</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>115986</t>
+          <t>117582</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>152654</t>
+          <t>153048</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7527</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>20054</t>
+          <t>19521</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6807</t>
+          <t>6996</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>17821</t>
+          <t>18066</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>17707</t>
+          <t>17071</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>33627</t>
+          <t>33683</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1582</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7356</t>
+          <t>7762</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>2394</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9437</t>
+          <t>9264</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>109482</t>
+          <t>108826</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>117392</t>
+          <t>117006</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105886</t>
+          <t>105801</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>112713</t>
+          <t>112799</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>218087</t>
+          <t>218206</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>228271</t>
+          <t>228673</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1458</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>7171</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3651</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11548</t>
+          <t>11973</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2587</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9728</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4190</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13923</t>
+          <t>14741</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8445</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20686</t>
+          <t>20118</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>164144</t>
+          <t>164243</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>176625</t>
+          <t>176798</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>198348</t>
+          <t>199085</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>212402</t>
+          <t>212320</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>366690</t>
+          <t>368104</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>385704</t>
+          <t>386184</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,68%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16372</t>
+          <t>15576</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14903</t>
+          <t>14478</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12725</t>
+          <t>12630</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26112</t>
+          <t>26166</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>565</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>3985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>602</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5977</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2491</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11428</t>
+          <t>11521</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18556</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11714</t>
+          <t>11698</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25950</t>
+          <t>25073</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>134425</t>
+          <t>134844</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>149055</t>
+          <t>149179</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>129424</t>
+          <t>129737</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>145991</t>
+          <t>145932</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>270847</t>
+          <t>269925</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>293158</t>
+          <t>293154</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,38%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>9706</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21236</t>
+          <t>21644</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9587</t>
+          <t>9900</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22329</t>
+          <t>22040</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22372</t>
+          <t>22131</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38884</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>6931</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11418</t>
+          <t>11345</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>5313</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14902</t>
+          <t>14698</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12366</t>
+          <t>11388</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26214</t>
+          <t>24607</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19377</t>
+          <t>19626</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36074</t>
+          <t>34907</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>119822</t>
+          <t>119906</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>135158</t>
+          <t>136026</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>108997</t>
+          <t>110318</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>127652</t>
+          <t>129210</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>235038</t>
+          <t>235637</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>260375</t>
+          <t>260210</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,11%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11949</t>
+          <t>11327</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24454</t>
+          <t>25164</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13222</t>
+          <t>13066</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27451</t>
+          <t>27400</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>28855</t>
+          <t>28403</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>48005</t>
+          <t>47310</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7289</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8983</t>
+          <t>9335</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17331</t>
+          <t>17697</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32808</t>
+          <t>32592</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>30183</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>50537</t>
+          <t>50011</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>52051</t>
+          <t>50880</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>78626</t>
+          <t>77021</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>543558</t>
+          <t>543039</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>568704</t>
+          <t>568829</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>559076</t>
+          <t>558800</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>588912</t>
+          <t>589545</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1110906</t>
+          <t>1109985</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1149891</t>
+          <t>1150956</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,49%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>37503</t>
+          <t>36429</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>57350</t>
+          <t>57137</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>36674</t>
+          <t>36128</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58248</t>
+          <t>59487</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>77666</t>
+          <t>79374</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>108343</t>
+          <t>110206</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>11478</t>
+          <t>11189</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11437</t>
+          <t>11672</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>19699</t>
+          <t>20111</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>530</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>532</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5974</t>
+          <t>5653</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50059</t>
+          <t>50149</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56103</t>
+          <t>56224</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53306</t>
+          <t>53555</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59367</t>
+          <t>59282</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106642</t>
+          <t>106356</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>114423</t>
+          <t>114492</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>410</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2496</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8887</t>
+          <t>9070</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16923</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>6724</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19351</t>
+          <t>19073</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>15619</t>
+          <t>15978</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>30683</t>
+          <t>32062</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>134060</t>
+          <t>134798</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>147756</t>
+          <t>147646</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>148990</t>
+          <t>148327</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>164185</t>
+          <t>164530</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>289960</t>
+          <t>288149</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>309568</t>
+          <t>309256</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,65%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2678</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12746</t>
+          <t>12334</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>6747</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17285</t>
+          <t>17840</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11655</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>25632</t>
+          <t>25501</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>829</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10912,7 +10912,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>320</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12825</t>
+          <t>12482</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31669</t>
+          <t>30222</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8984</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23428</t>
+          <t>22961</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25304</t>
+          <t>25461</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48434</t>
+          <t>50785</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>120626</t>
+          <t>120806</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>141843</t>
+          <t>141692</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>162259</t>
+          <t>162493</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>183169</t>
+          <t>183904</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>289091</t>
+          <t>289473</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>320173</t>
+          <t>321129</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,62%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11990</t>
+          <t>11699</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26312</t>
+          <t>25321</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14773</t>
+          <t>14687</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31825</t>
+          <t>31607</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30689</t>
+          <t>30185</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51721</t>
+          <t>52530</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>4547</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11461,7 +11461,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5542</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>695</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6432</t>
+          <t>6581</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>16595</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33903</t>
+          <t>35789</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31072</t>
+          <t>31329</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63842</t>
+          <t>62093</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>53696</t>
+          <t>51235</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>88478</t>
+          <t>88760</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>210934</t>
+          <t>209916</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239229</t>
+          <t>238098</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>211880</t>
+          <t>215312</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>250154</t>
+          <t>251933</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>434982</t>
+          <t>435480</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>481695</t>
+          <t>483141</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,64%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10264</t>
+          <t>9835</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25848</t>
+          <t>25252</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11774</t>
+          <t>11833</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>38372</t>
+          <t>37681</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>26242</t>
+          <t>27146</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>56546</t>
+          <t>56693</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15403</t>
+          <t>14780</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1752</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>9707</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21213</t>
+          <t>22069</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>45478</t>
+          <t>44761</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>73197</t>
+          <t>72193</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>54652</t>
+          <t>54868</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>90386</t>
+          <t>90894</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>109578</t>
+          <t>107332</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>155151</t>
+          <t>153524</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>533826</t>
+          <t>533098</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>571121</t>
+          <t>570763</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>601400</t>
+          <t>597744</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>646419</t>
+          <t>645724</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1143178</t>
+          <t>1143279</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1202516</t>
+          <t>1204464</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,75%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31091</t>
+          <t>33273</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>55606</t>
+          <t>56373</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>43742</t>
+          <t>44650</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>74933</t>
+          <t>75901</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>82574</t>
+          <t>83015</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>121320</t>
+          <t>121802</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17119</t>
+          <t>16868</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>13771</t>
+          <t>13517</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12634,7 +12634,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>10463</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>25233</t>
+          <t>25992</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
